--- a/rules/CORE-000886/positive/01/data/unit-test-coreid-FB2306-positive.xlsx
+++ b/rules/CORE-000886/positive/01/data/unit-test-coreid-FB2306-positive.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sanofinam-my.sharepoint.com/personal/malini_narreddy_sanofi_com/Documents/Desktop/Imp links/SDTM CIDSC documents/CDISC CORE project/FB2306/positive/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000886\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="8_{2FA9E1B7-D453-41A5-80B4-20CD2E4EF959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{654AF18F-9E3C-43A2-A3D6-529915BDAB80}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3861D32F-92C1-4B3D-ACF0-40A366B74F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="55545" yWindow="705" windowWidth="23865" windowHeight="17250" activeTab="3" xr2:uid="{E84A5625-D8F6-4FB6-94ED-5413F497365D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E84A5625-D8F6-4FB6-94ED-5413F497365D}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="4" r:id="rId1"/>
@@ -745,7 +745,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -761,12 +761,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -829,7 +823,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -884,16 +878,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1311,9 +1302,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D5C60B-7D2C-4EC2-90C9-FC331856666A}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1321,7 +1312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1337,13 +1328,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C5DEA90-A259-4FF8-84C3-0BEFD4EAEE66}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1351,7 +1342,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>208</v>
       </c>
@@ -1359,7 +1350,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1367,7 +1358,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1384,13 +1375,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7FF5D75-689C-4B29-A8B9-150A10FE1AF9}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="11" width="20.7265625" style="14" customWidth="1"/>
-    <col min="12" max="16384" width="8.81640625" style="15"/>
+    <col min="1" max="11" width="20.7109375" style="14" customWidth="1"/>
+    <col min="12" max="16384" width="8.85546875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>9</v>
       </c>
@@ -1425,7 +1416,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="14" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
@@ -1460,7 +1451,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>43</v>
       </c>
@@ -1495,7 +1486,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>216</v>
       </c>
@@ -1530,7 +1521,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>45</v>
       </c>
@@ -1555,7 +1546,7 @@
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
     </row>
-    <row r="6" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>45</v>
       </c>
@@ -1586,7 +1577,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>45</v>
       </c>
@@ -1617,7 +1608,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>45</v>
       </c>
@@ -1642,7 +1633,7 @@
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
     </row>
-    <row r="9" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>45</v>
       </c>
@@ -1667,7 +1658,7 @@
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>45</v>
       </c>
@@ -1700,7 +1691,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>45</v>
       </c>
@@ -1733,7 +1724,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>45</v>
       </c>
@@ -1760,7 +1751,7 @@
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
     </row>
-    <row r="13" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>45</v>
       </c>
@@ -1787,7 +1778,7 @@
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
     </row>
-    <row r="14" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>45</v>
       </c>
@@ -1798,13 +1789,13 @@
         <v>157</v>
       </c>
       <c r="D14" s="17"/>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="24" t="s">
         <v>192</v>
       </c>
       <c r="H14" s="17"/>
@@ -1818,7 +1809,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>45</v>
       </c>
@@ -1849,7 +1840,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>45</v>
       </c>
@@ -1880,7 +1871,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="18" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>45</v>
       </c>
@@ -1922,26 +1913,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{795E7702-96E4-4A0E-BB7C-F4A9CD306A5D}">
   <dimension ref="A1:AA10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
-    <col min="4" max="4" width="14.54296875" customWidth="1"/>
-    <col min="5" max="5" width="19.54296875" customWidth="1"/>
+    <col min="1" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" customWidth="1"/>
-    <col min="9" max="9" width="17.1796875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="16.1796875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.453125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" hidden="1" customWidth="1"/>
     <col min="12" max="13" width="0" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="12.81640625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" hidden="1" customWidth="1"/>
     <col min="15" max="19" width="0" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="17.26953125" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="15.81640625" customWidth="1"/>
+    <col min="20" max="20" width="17.28515625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2024,7 +2015,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -2107,7 +2098,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>43</v>
       </c>
@@ -2190,7 +2181,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>12</v>
       </c>
@@ -2273,14 +2264,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
       <c r="B5" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="22" t="s">
         <v>211</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -2334,7 +2325,7 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
-      <c r="Y5" s="23" t="s">
+      <c r="Y5" s="22" t="s">
         <v>220</v>
       </c>
       <c r="Z5" s="1"/>
@@ -2342,14 +2333,14 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>45</v>
       </c>
       <c r="B6" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>212</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -2405,7 +2396,7 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
-      <c r="Y6" s="23" t="s">
+      <c r="Y6" s="22" t="s">
         <v>219</v>
       </c>
       <c r="Z6" s="1"/>
@@ -2413,14 +2404,14 @@
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="1:27" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>45</v>
       </c>
       <c r="B7" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>213</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2480,7 +2471,7 @@
       </c>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
-      <c r="Y7" s="23" t="s">
+      <c r="Y7" s="22" t="s">
         <v>218</v>
       </c>
       <c r="Z7" s="1"/>
@@ -2488,7 +2479,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -2557,13 +2548,13 @@
       <c r="X8" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="Y8" s="24"/>
+      <c r="Y8" s="22"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -2634,13 +2625,13 @@
       <c r="X9" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="Y9" s="24"/>
+      <c r="Y9" s="22"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -2711,7 +2702,7 @@
       <c r="X10" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="Y10" s="24"/>
+      <c r="Y10" s="22"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1" t="s">
         <v>135</v>
@@ -2734,16 +2725,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FFAAC06-8AA1-4098-9728-071939A44F17}">
   <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="24.7265625" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" customWidth="1"/>
-    <col min="10" max="10" width="27.1796875" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="27.140625" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="16.81640625" customWidth="1"/>
+    <col min="16" max="16" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
@@ -2799,7 +2790,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
@@ -2855,7 +2846,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>43</v>
       </c>
@@ -2911,7 +2902,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>216</v>
       </c>
@@ -2967,14 +2958,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
       <c r="B5" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="22" t="s">
         <v>47</v>
       </c>
       <c r="D5">
@@ -3020,14 +3011,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>45</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="22" t="s">
         <v>55</v>
       </c>
       <c r="D6">
@@ -3067,14 +3058,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>45</v>
       </c>
       <c r="B7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="22" t="s">
         <v>214</v>
       </c>
       <c r="D7">
@@ -3114,8 +3105,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C8" s="25"/>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C8" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3123,20 +3114,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3363,19 +3354,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A58D54F7-511B-43F8-921F-D11D7692FD68}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70C9EDA2-6184-4936-95C4-1B27C2EDFE85}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70C9EDA2-6184-4936-95C4-1B27C2EDFE85}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A58D54F7-511B-43F8-921F-D11D7692FD68}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
